--- a/public/template_simpanan.xlsx
+++ b/public/template_simpanan.xlsx
@@ -418,7 +418,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>001</v>
+        <v>1</v>
       </c>
       <c r="B2" t="str">
         <v>Contoh Anggota 1</v>
@@ -435,7 +435,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>002</v>
+        <v>2</v>
       </c>
       <c r="B3" t="str">
         <v>Contoh Anggota 2</v>

--- a/public/template_simpanan.xlsx
+++ b/public/template_simpanan.xlsx
@@ -427,7 +427,7 @@
         <v>100000</v>
       </c>
       <c r="D2" t="str">
-        <v>2024-01-15</v>
+        <v>15-01-2024</v>
       </c>
       <c r="E2" t="str">
         <v>aktif</v>
@@ -444,7 +444,7 @@
         <v>50000</v>
       </c>
       <c r="D3" t="str">
-        <v>2024-01-16</v>
+        <v>16-01-2024</v>
       </c>
       <c r="E3" t="str">
         <v>aktif</v>
